--- a/output/2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Attiva da oltre 25 anni, produzione confermata da più fonti (fininfo.hr, kompass, sito ufficiale). Sede fuori contea target.</t>
+          <t>Attiva da oltre 25 anni, produzione confermata da più fonti (fininfo.hr, kompass, sito ufficiale). Sede fuori contea target. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,10 +704,9 @@
           <t>+385 1 2910 110</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Azienda dal 1992, certificazioni ISO 9001/14001 confermate. Sede fuori contea target.</t>
+          <t>Azienda dal 1992, certificazioni ISO 9001/14001 confermate. Sede fuori contea target. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -749,7 +748,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Filiale del gruppo internazionale HENNLICH, ampio catalogo tecnico confermato sul sito ufficiale. Sede fuori contea target.</t>
+          <t>Filiale del gruppo internazionale HENNLICH, ampio catalogo tecnico confermato sul sito ufficiale. Sede fuori contea target. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -791,7 +790,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Filiale croata del produttore tedesco BerlinerLuft.Technik GmbH; produttore/national branch con rete di distribuzione, non puro rivenditore terzo. Sede fuori contea target.</t>
+          <t>Filiale croata del produttore tedesco BerlinerLuft.Technik GmbH; produttore/national branch con rete di distribuzione, non puro rivenditore terzo. Sede fuori contea target. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -875,7 +874,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Azienda dal 1991, 501-1000 dipendenti, rete di negozi confermata su più fonti. Sede fuori contea target.</t>
+          <t>Azienda dal 1991, 501-1000 dipendenti, rete di negozi confermata su più fonti. Sede fuori contea target. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -917,7 +916,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Catalogo online con ampia gamma di componenti spiro/ventilazione confermato. Contea confinante con quella target.</t>
+          <t>Catalogo online con ampia gamma di componenti spiro/ventilazione confermato. Contea confinante con quella target. [DUPLICATO — vedi anche: 2026-09-08_02_Croazia_Krapinsko-zagorska_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -959,7 +958,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Produttore specializzato, vende tramite canale commerciale a installatori/rivenditori. Sede fuori contea target.</t>
+          <t>Produttore specializzato, vende tramite canale commerciale a installatori/rivenditori. Sede fuori contea target. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">

--- a/output/2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
